--- a/imerg_3hr.xlsx
+++ b/imerg_3hr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Damius\Documents\Palawan_Shear_Line\Palawan_Shear_Line\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B5A997-8122-4F47-B7F5-4591F291E110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426BBAB4-AB69-4B08-AC9A-546DB31E5853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{A1EB678B-CB49-46E6-BA70-D9F7025CB109}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Time</t>
   </si>
@@ -39,79 +39,43 @@
     <t>IMERG</t>
   </si>
   <si>
-    <t>Station</t>
-  </si>
-  <si>
-    <t>07_03</t>
-  </si>
-  <si>
     <t>07_06</t>
-  </si>
-  <si>
-    <t>07_09</t>
   </si>
   <si>
     <t>07_12</t>
   </si>
   <si>
-    <t>07_15</t>
-  </si>
-  <si>
     <t>07_18</t>
-  </si>
-  <si>
-    <t>07_21</t>
   </si>
   <si>
     <t>08_00</t>
   </si>
   <si>
-    <t>08_03</t>
-  </si>
-  <si>
     <t>08_06</t>
-  </si>
-  <si>
-    <t>08_09</t>
   </si>
   <si>
     <t>08_12</t>
   </si>
   <si>
-    <t>08_15</t>
-  </si>
-  <si>
     <t>08_18</t>
-  </si>
-  <si>
-    <t>08_21</t>
   </si>
   <si>
     <t>09_00</t>
   </si>
   <si>
-    <t>09_03</t>
-  </si>
-  <si>
     <t>09_06</t>
-  </si>
-  <si>
-    <t>09_09</t>
   </si>
   <si>
     <t>09_12</t>
   </si>
   <si>
-    <t>09_15</t>
-  </si>
-  <si>
     <t>09_18</t>
   </si>
   <si>
-    <t>09_21</t>
+    <t>10_00</t>
   </si>
   <si>
-    <t>09_24</t>
+    <t>OBS</t>
   </si>
 </sst>
 </file>
@@ -659,6 +623,1275 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>imerg_3hr!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>IMERG</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>imerg_3hr!$A$2:$A$25</c:f>
+              <c:strCache>
+                <c:ptCount val="24"/>
+                <c:pt idx="1">
+                  <c:v>07_06</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>07_12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>07_18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>08_00</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>08_06</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>08_12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>08_18</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>09_00</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>09_06</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>09_12</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>09_18</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>10_00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>imerg_3hr!$B$2:$B$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>3.34</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.69</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.47</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>19.739999999999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>97.25</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90.56</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>22.27</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>32.33</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>66.61</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.18</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>25.79</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>17.46</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>35.32</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>103.33</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>81.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>39.159999999999997</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46.15</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>42.41</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>90.19</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>50.63</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>35.700000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4C92-44E4-A95B-BB82970D120C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>imerg_3hr!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>OBS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>imerg_3hr!$A$2:$A$25</c:f>
+              <c:strCache>
+                <c:ptCount val="24"/>
+                <c:pt idx="1">
+                  <c:v>07_06</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>07_12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>07_18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>08_00</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>08_06</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>08_12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>08_18</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>09_00</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>09_06</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>09_12</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>09_18</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>10_00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>imerg_3hr!$C$2:$C$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4C92-44E4-A95B-BB82970D120C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1704686335"/>
+        <c:axId val="1704684895"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1704686335"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Time (day_hour,</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> UTC)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="out"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1704684895"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1704684895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Accumulated</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Rainfall (mm/3h)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1704686335"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>91440</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FB24458-3805-962F-CA35-0852FB8F4135}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -972,13 +2205,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
       <c r="B2">
         <v>3.34</v>
       </c>
@@ -988,7 +2218,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -998,9 +2228,6 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
       <c r="B4">
         <v>0.26</v>
       </c>
@@ -1010,7 +2237,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>9.69</v>
@@ -1020,9 +2247,6 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
       <c r="B6">
         <v>0</v>
       </c>
@@ -1032,7 +2256,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B7">
         <v>0.47</v>
@@ -1042,9 +2266,6 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
       <c r="B8">
         <v>19.739999999999998</v>
       </c>
@@ -1054,7 +2275,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B9">
         <v>97.25</v>
@@ -1064,9 +2285,6 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
       <c r="B10">
         <v>90.56</v>
       </c>
@@ -1076,7 +2294,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B11">
         <v>22.27</v>
@@ -1086,9 +2304,6 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
       <c r="B12">
         <v>32.33</v>
       </c>
@@ -1098,7 +2313,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B13">
         <v>66.61</v>
@@ -1108,9 +2323,6 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
       <c r="B14">
         <v>6.18</v>
       </c>
@@ -1120,7 +2332,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B15">
         <v>25.79</v>
@@ -1130,9 +2342,6 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
       <c r="B16">
         <v>17.46</v>
       </c>
@@ -1142,7 +2351,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B17">
         <v>35.32</v>
@@ -1152,9 +2361,6 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
       <c r="B18">
         <v>103.33</v>
       </c>
@@ -1164,7 +2370,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B19">
         <v>81.900000000000006</v>
@@ -1174,9 +2380,6 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
       <c r="B20">
         <v>39.159999999999997</v>
       </c>
@@ -1186,7 +2389,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B21">
         <v>46.15</v>
@@ -1196,9 +2399,6 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
       <c r="B22">
         <v>42.41</v>
       </c>
@@ -1208,7 +2408,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B23">
         <v>90.19</v>
@@ -1218,9 +2418,6 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>25</v>
-      </c>
       <c r="B24">
         <v>50.63</v>
       </c>
@@ -1230,7 +2427,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B25">
         <v>35.700000000000003</v>
@@ -1252,5 +2449,6 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/imerg_3hr.xlsx
+++ b/imerg_3hr.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Damius\Documents\Palawan_Shear_Line\Palawan_Shear_Line\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DJEV\Documents\Palawan_Shear_Line\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426BBAB4-AB69-4B08-AC9A-546DB31E5853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A62E470-408C-4DEA-B509-9F15625D4818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{A1EB678B-CB49-46E6-BA70-D9F7025CB109}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{A1EB678B-CB49-46E6-BA70-D9F7025CB109}"/>
   </bookViews>
   <sheets>
     <sheet name="imerg_3hr" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
   <si>
     <t>Time</t>
   </si>
@@ -76,6 +77,66 @@
   </si>
   <si>
     <t>OBS</t>
+  </si>
+  <si>
+    <t>09_01</t>
+  </si>
+  <si>
+    <t>09_02</t>
+  </si>
+  <si>
+    <t>09_03</t>
+  </si>
+  <si>
+    <t>09_04</t>
+  </si>
+  <si>
+    <t>09_05</t>
+  </si>
+  <si>
+    <t>09_07</t>
+  </si>
+  <si>
+    <t>09_08</t>
+  </si>
+  <si>
+    <t>09_09</t>
+  </si>
+  <si>
+    <t>09_10</t>
+  </si>
+  <si>
+    <t>09_11</t>
+  </si>
+  <si>
+    <t>09_13</t>
+  </si>
+  <si>
+    <t>09_14</t>
+  </si>
+  <si>
+    <t>09_15</t>
+  </si>
+  <si>
+    <t>09_16</t>
+  </si>
+  <si>
+    <t>09_17</t>
+  </si>
+  <si>
+    <t>09_19</t>
+  </si>
+  <si>
+    <t>09_20</t>
+  </si>
+  <si>
+    <t>09_21</t>
+  </si>
+  <si>
+    <t>09_22</t>
+  </si>
+  <si>
+    <t>09_23</t>
   </si>
 </sst>
 </file>
@@ -2192,12 +2253,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{486EE33A-36C3-493C-ABC8-35286F860A06}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2208,7 +2269,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2">
         <v>3.34</v>
       </c>
@@ -2216,7 +2277,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2227,7 +2288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>0.26</v>
       </c>
@@ -2235,7 +2296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2246,7 +2307,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>0</v>
       </c>
@@ -2254,7 +2315,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -2265,7 +2326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>19.739999999999998</v>
       </c>
@@ -2273,7 +2334,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -2284,7 +2345,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>90.56</v>
       </c>
@@ -2292,7 +2353,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -2303,7 +2364,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>32.33</v>
       </c>
@@ -2311,7 +2372,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -2322,7 +2383,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>6.18</v>
       </c>
@@ -2330,7 +2391,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -2341,7 +2402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>17.46</v>
       </c>
@@ -2349,7 +2410,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -2360,7 +2421,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>103.33</v>
       </c>
@@ -2368,7 +2429,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -2379,7 +2440,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>39.159999999999997</v>
       </c>
@@ -2387,7 +2448,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -2398,7 +2459,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>42.41</v>
       </c>
@@ -2406,7 +2467,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -2417,7 +2478,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>50.63</v>
       </c>
@@ -2425,7 +2486,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -2436,7 +2497,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B26">
         <f>SUM(B2:B25)</f>
         <v>916.7399999999999</v>
@@ -2451,4 +2512,376 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1855A55-AE8C-4B24-8657-B032129A7CD0}">
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>8.5</v>
+      </c>
+      <c r="C2">
+        <v>7.7</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3">
+        <v>15.5</v>
+      </c>
+      <c r="C3">
+        <v>1.7</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5">
+        <v>3.1</v>
+      </c>
+      <c r="C5">
+        <v>0.1</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <v>0.2</v>
+      </c>
+      <c r="C7">
+        <v>0.7</v>
+      </c>
+      <c r="D7">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>0.5</v>
+      </c>
+      <c r="C8">
+        <v>0.2</v>
+      </c>
+      <c r="D8">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
+        <v>0.6</v>
+      </c>
+      <c r="C10">
+        <v>1.4</v>
+      </c>
+      <c r="D10">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
+        <v>1.3</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
+        <v>0.1</v>
+      </c>
+      <c r="C12">
+        <v>0.5</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>0.7</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19">
+        <v>0.2</v>
+      </c>
+      <c r="C19">
+        <v>0.1</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0.1</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22">
+        <v>0.3</v>
+      </c>
+      <c r="C22">
+        <v>4.5</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23">
+        <v>0.6</v>
+      </c>
+      <c r="C23">
+        <v>1.7</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24">
+        <v>0.1</v>
+      </c>
+      <c r="C24">
+        <v>0.3</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25">
+        <v>0.1</v>
+      </c>
+      <c r="C25">
+        <v>0.9</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>